--- a/artfynd/A 42936-2024 artfynd.xlsx
+++ b/artfynd/A 42936-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7045046</v>
       </c>
       <c r="B2" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725646.9040449342</v>
+        <v>725647</v>
       </c>
       <c r="R2" t="n">
-        <v>6396857.65331762</v>
+        <v>6396858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2013-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,42 +783,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7045045</v>
+        <v>7045042</v>
       </c>
       <c r="B3" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249228</v>
+        <v>2015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725611.4465401582</v>
+        <v>725611</v>
       </c>
       <c r="R3" t="n">
-        <v>6396973.095993224</v>
+        <v>6396973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,19 +861,9 @@
           <t>2013-10-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,42 +891,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7045047</v>
+        <v>7045043</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -971,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725646.9040449342</v>
+        <v>725611</v>
       </c>
       <c r="R4" t="n">
-        <v>6396857.65331762</v>
+        <v>6396973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,19 +969,9 @@
           <t>2013-10-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7045043</v>
+        <v>7045047</v>
       </c>
       <c r="B5" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,26 +1010,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725611.4465401582</v>
+        <v>725647</v>
       </c>
       <c r="R5" t="n">
-        <v>6396973.095993224</v>
+        <v>6396858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1077,9 @@
           <t>2013-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-10-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,42 +1107,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7045042</v>
+        <v>7045045</v>
       </c>
       <c r="B6" t="n">
-        <v>89175</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2015</v>
+        <v>249228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1217,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725611.4465401582</v>
+        <v>725611</v>
       </c>
       <c r="R6" t="n">
-        <v>6396973.095993224</v>
+        <v>6396973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,19 +1185,9 @@
           <t>2013-10-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-10-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42936-2024 artfynd.xlsx
+++ b/artfynd/A 42936-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7045046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7045042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7045043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7045047</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,8 +1237,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7045045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>